--- a/server/xlsx/怪物表.xlsx
+++ b/server/xlsx/怪物表.xlsx
@@ -4,13 +4,14 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255" activeTab="1"/>
+    <workbookView windowWidth="21720" windowHeight="9870" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="map_enemy" sheetId="1" r:id="rId1"/>
-    <sheet name="map_enemy_pet" sheetId="4" r:id="rId2"/>
-    <sheet name="map_enemy (2)" sheetId="2" r:id="rId3"/>
-    <sheet name="map_enemy (3)" sheetId="3" r:id="rId4"/>
+    <sheet name="map_主神空间" sheetId="1" r:id="rId1"/>
+    <sheet name="map_测试地图" sheetId="5" r:id="rId2"/>
+    <sheet name="map_测试地图2" sheetId="4" r:id="rId3"/>
+    <sheet name="map_enemy (2)" sheetId="2" r:id="rId4"/>
+    <sheet name="map_enemy (3)" sheetId="3" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="96">
   <si>
     <t>id</t>
   </si>
@@ -1276,7 +1277,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="黑色浅色系标题行表格样式" count="2" xr9:uid="{C4A1F62E-6D4F-4F7C-9055-082FF87BE709}">
+    <tableStyle name="黑色浅色系标题行表格样式" count="2" xr9:uid="{9595FD8C-6A3A-4F40-95A6-432E0658E3F0}">
       <tableStyleElement type="wholeTable" dxfId="1"/>
       <tableStyleElement type="headerRow" dxfId="0"/>
     </tableStyle>
@@ -1651,6 +1652,81 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="3"/>
+  <cols>
+    <col min="1" max="1" width="9.84166666666667" customWidth="1"/>
+    <col min="2" max="2" width="12.3416666666667" customWidth="1"/>
+    <col min="3" max="3" width="10.3416666666667" customWidth="1"/>
+    <col min="4" max="4" width="20.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22.5" customHeight="1" spans="1:4">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" ht="22.5" customHeight="1" spans="1:4">
+      <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" ht="22.5" customHeight="1" spans="1:4">
+      <c r="A3" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" ht="22.5" customHeight="1" spans="1:4">
+      <c r="A4" s="7">
+        <v>1</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="8">
+        <v>17</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:D13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
@@ -1850,7 +1926,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D16"/>
@@ -2093,7 +2169,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E31"/>

--- a/server/xlsx/怪物表.xlsx
+++ b/server/xlsx/怪物表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21720" windowHeight="9870" activeTab="1"/>
+    <workbookView windowWidth="31950" windowHeight="9870" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="map_主神空间" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="98">
   <si>
     <t>id</t>
   </si>
@@ -61,6 +61,13 @@
   </si>
   <si>
     <t>普通攻击-木头撞击</t>
+  </si>
+  <si>
+    <t>sk_active</t>
+  </si>
+  <si>
+    <t>普通攻击as木头撞击
+普通攻击as冲撞</t>
   </si>
   <si>
     <t>可莉</t>
@@ -1277,7 +1284,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="黑色浅色系标题行表格样式" count="2" xr9:uid="{9595FD8C-6A3A-4F40-95A6-432E0658E3F0}">
+    <tableStyle name="黑色浅色系标题行表格样式" count="2" xr9:uid="{1328B46F-2DFD-46DD-A77F-E8A23379C35A}">
       <tableStyleElement type="wholeTable" dxfId="1"/>
       <tableStyleElement type="headerRow" dxfId="0"/>
     </tableStyle>
@@ -1658,7 +1665,7 @@
     <col min="1" max="1" width="9.84166666666667" customWidth="1"/>
     <col min="2" max="2" width="12.3416666666667" customWidth="1"/>
     <col min="3" max="3" width="10.3416666666667" customWidth="1"/>
-    <col min="4" max="4" width="20.625" customWidth="1"/>
+    <col min="4" max="4" width="18.25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="22.5" customHeight="1" spans="1:4">
@@ -1686,7 +1693,7 @@
         <v>5</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" ht="22.5" customHeight="1" spans="1:4">
@@ -1703,7 +1710,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" ht="22.5" customHeight="1" spans="1:4">
+    <row r="4" ht="39" customHeight="1" spans="1:4">
       <c r="A4" s="7">
         <v>1</v>
       </c>
@@ -1714,7 +1721,7 @@
         <v>17</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1784,13 +1791,13 @@
         <v>1</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D4" s="20" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" ht="39" customHeight="1" spans="1:4">
@@ -1798,13 +1805,13 @@
         <v>2</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" ht="39" customHeight="1" spans="1:4">
@@ -1812,13 +1819,13 @@
         <v>3</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D6" s="21" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1826,13 +1833,13 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C7" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D7" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1840,13 +1847,13 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C8" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D8" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1854,13 +1861,13 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D9" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1868,13 +1875,13 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D10" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1882,13 +1889,13 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C11" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D11" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1896,13 +1903,13 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C12" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D12" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1910,13 +1917,13 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C13" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D13" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -1985,13 +1992,13 @@
         <v>1</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C4" s="8">
         <v>1</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" ht="22.5" customHeight="1" spans="1:4">
@@ -1999,13 +2006,13 @@
         <v>2</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C5" s="8">
         <v>2</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" ht="22.5" customHeight="1" spans="1:4">
@@ -2013,13 +2020,13 @@
         <v>3</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C6" s="8">
         <v>3</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7" ht="22.5" customHeight="1" spans="1:4">
@@ -2027,13 +2034,13 @@
         <v>4</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C7" s="8">
         <v>4</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8" ht="22.5" customHeight="1" spans="1:4">
@@ -2041,13 +2048,13 @@
         <v>5</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C8" s="8">
         <v>5</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" ht="36" customHeight="1" spans="1:4">
@@ -2055,13 +2062,13 @@
         <v>6</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C9" s="8">
         <v>6</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" ht="22.5" customHeight="1" spans="1:4">
@@ -2069,13 +2076,13 @@
         <v>7</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C10" s="8">
         <v>7</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11" ht="22.5" customHeight="1" spans="1:4">
@@ -2083,13 +2090,13 @@
         <v>8</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C11" s="8">
         <v>8</v>
       </c>
       <c r="D11" s="17" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="12" ht="22.5" customHeight="1" spans="1:4">
@@ -2097,13 +2104,13 @@
         <v>9</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C12" s="8">
         <v>9</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="13" ht="28" customHeight="1" spans="1:4">
@@ -2111,13 +2118,13 @@
         <v>10</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C13" s="8">
         <v>10</v>
       </c>
       <c r="D13" s="17" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2125,13 +2132,13 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C14">
         <v>12</v>
       </c>
       <c r="D14" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2139,13 +2146,13 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C15">
         <v>13</v>
       </c>
       <c r="D15" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:4">
@@ -2153,13 +2160,13 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C16">
         <v>14</v>
       </c>
       <c r="D16" s="17" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -2193,7 +2200,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>3</v>
@@ -2210,7 +2217,7 @@
         <v>5</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E2" s="4" t="s">
         <v>6</v>
@@ -2227,7 +2234,7 @@
         <v>7</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>7</v>
@@ -2238,7 +2245,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C4" s="8">
         <v>11</v>
@@ -2247,7 +2254,7 @@
         <v>1</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -2255,7 +2262,7 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C5">
         <v>15</v>
@@ -2264,7 +2271,7 @@
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -2272,7 +2279,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C6">
         <v>16</v>
@@ -2281,7 +2288,7 @@
         <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -2289,7 +2296,7 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C7">
         <v>16</v>
@@ -2298,7 +2305,7 @@
         <v>1</v>
       </c>
       <c r="E7" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -2306,7 +2313,7 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C8">
         <v>16</v>
@@ -2315,7 +2322,7 @@
         <v>1</v>
       </c>
       <c r="E8" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -2323,7 +2330,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C9">
         <v>16</v>
@@ -2332,7 +2339,7 @@
         <v>1</v>
       </c>
       <c r="E9" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -2340,7 +2347,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C10">
         <v>16</v>
@@ -2349,7 +2356,7 @@
         <v>1</v>
       </c>
       <c r="E10" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -2357,7 +2364,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C11">
         <v>16</v>
@@ -2366,7 +2373,7 @@
         <v>1</v>
       </c>
       <c r="E11" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -2374,7 +2381,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C12">
         <v>16</v>
@@ -2383,7 +2390,7 @@
         <v>1</v>
       </c>
       <c r="E12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -2391,7 +2398,7 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C13">
         <v>16</v>
@@ -2400,7 +2407,7 @@
         <v>1</v>
       </c>
       <c r="E13" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -2408,7 +2415,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C14">
         <v>16</v>
@@ -2417,7 +2424,7 @@
         <v>1</v>
       </c>
       <c r="E14" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -2425,7 +2432,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C15">
         <v>16</v>
@@ -2434,7 +2441,7 @@
         <v>1</v>
       </c>
       <c r="E15" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -2442,7 +2449,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C16">
         <v>16</v>
@@ -2451,7 +2458,7 @@
         <v>1</v>
       </c>
       <c r="E16" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -2459,7 +2466,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C17">
         <v>16</v>
@@ -2468,7 +2475,7 @@
         <v>1</v>
       </c>
       <c r="E17" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -2476,7 +2483,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C18">
         <v>16</v>
@@ -2485,7 +2492,7 @@
         <v>1</v>
       </c>
       <c r="E18" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -2493,7 +2500,7 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C19">
         <v>16</v>
@@ -2502,7 +2509,7 @@
         <v>1</v>
       </c>
       <c r="E19" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -2510,7 +2517,7 @@
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C20">
         <v>16</v>
@@ -2519,7 +2526,7 @@
         <v>1</v>
       </c>
       <c r="E20" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -2527,7 +2534,7 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C21">
         <v>16</v>
@@ -2536,7 +2543,7 @@
         <v>1</v>
       </c>
       <c r="E21" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -2544,7 +2551,7 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C22">
         <v>16</v>
@@ -2553,7 +2560,7 @@
         <v>1</v>
       </c>
       <c r="E22" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -2561,7 +2568,7 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C23">
         <v>16</v>
@@ -2570,7 +2577,7 @@
         <v>1</v>
       </c>
       <c r="E23" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -2578,7 +2585,7 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C24">
         <v>16</v>
@@ -2587,7 +2594,7 @@
         <v>1</v>
       </c>
       <c r="E24" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -2595,7 +2602,7 @@
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C25">
         <v>16</v>
@@ -2604,7 +2611,7 @@
         <v>1</v>
       </c>
       <c r="E25" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -2612,7 +2619,7 @@
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C26">
         <v>16</v>
@@ -2621,7 +2628,7 @@
         <v>1</v>
       </c>
       <c r="E26" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -2629,7 +2636,7 @@
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C27">
         <v>16</v>
@@ -2638,7 +2645,7 @@
         <v>1</v>
       </c>
       <c r="E27" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -2646,7 +2653,7 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C28">
         <v>16</v>
@@ -2655,7 +2662,7 @@
         <v>1</v>
       </c>
       <c r="E28" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2663,7 +2670,7 @@
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C29">
         <v>16</v>
@@ -2672,7 +2679,7 @@
         <v>1</v>
       </c>
       <c r="E29" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2680,7 +2687,7 @@
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C30">
         <v>16</v>
@@ -2689,7 +2696,7 @@
         <v>1</v>
       </c>
       <c r="E30" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2697,7 +2704,7 @@
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C31">
         <v>16</v>
@@ -2706,7 +2713,7 @@
         <v>1</v>
       </c>
       <c r="E31" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>

--- a/server/xlsx/怪物表.xlsx
+++ b/server/xlsx/怪物表.xlsx
@@ -4,14 +4,15 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="31950" windowHeight="9870" activeTab="1"/>
+    <workbookView windowWidth="28215" windowHeight="11640" firstSheet="3" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="map_主神空间" sheetId="1" r:id="rId1"/>
     <sheet name="map_测试地图" sheetId="5" r:id="rId2"/>
-    <sheet name="map_测试地图2" sheetId="4" r:id="rId3"/>
-    <sheet name="map_enemy (2)" sheetId="2" r:id="rId4"/>
-    <sheet name="map_enemy (3)" sheetId="3" r:id="rId5"/>
+    <sheet name="mapCfg" sheetId="6" r:id="rId3"/>
+    <sheet name="map_测试地图2" sheetId="4" r:id="rId4"/>
+    <sheet name="map_enemy (2)" sheetId="2" r:id="rId5"/>
+    <sheet name="map_enemy (3)" sheetId="3" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="118">
   <si>
     <t>id</t>
   </si>
@@ -63,11 +64,74 @@
     <t>普通攻击-木头撞击</t>
   </si>
   <si>
+    <t>体系</t>
+  </si>
+  <si>
+    <t>主动技能</t>
+  </si>
+  <si>
+    <t>属性基数</t>
+  </si>
+  <si>
+    <t>sys</t>
+  </si>
+  <si>
     <t>sk_active</t>
   </si>
   <si>
+    <t>生命值</t>
+  </si>
+  <si>
+    <t>魔法</t>
+  </si>
+  <si>
+    <t>物理攻击</t>
+  </si>
+  <si>
+    <t>魔法攻击</t>
+  </si>
+  <si>
+    <t>物理防御</t>
+  </si>
+  <si>
+    <t>魔法防御</t>
+  </si>
+  <si>
+    <t>物理暴击率</t>
+  </si>
+  <si>
+    <t>魔法暴击率</t>
+  </si>
+  <si>
+    <t>Num</t>
+  </si>
+  <si>
+    <t>修仙</t>
+  </si>
+  <si>
     <t>普通攻击as木头撞击
-普通攻击as冲撞</t>
+普通攻击as木桩冲撞</t>
+  </si>
+  <si>
+    <t>地图名称</t>
+  </si>
+  <si>
+    <t>推荐等级</t>
+  </si>
+  <si>
+    <t>难度</t>
+  </si>
+  <si>
+    <t>leve</t>
+  </si>
+  <si>
+    <t>diff</t>
+  </si>
+  <si>
+    <t>主神空间</t>
+  </si>
+  <si>
+    <t>测试地图</t>
   </si>
   <si>
     <t>可莉</t>
@@ -233,9 +297,6 @@
   </si>
   <si>
     <t>lock</t>
-  </si>
-  <si>
-    <t>Num</t>
   </si>
   <si>
     <t>平民</t>
@@ -717,7 +778,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="19">
+  <borders count="25">
     <border>
       <left/>
       <right/>
@@ -860,6 +921,74 @@
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color theme="0"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FF595959"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="FF595959"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF5A5A5A"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFEBEBEB"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFEBEBEB"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFEBEBEB"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFEBEBEB"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFEBEBEB"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFEBEBEB"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFEBEBEB"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFEBEBEB"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFEBEBEB"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -983,7 +1112,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="17" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -995,34 +1124,34 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="23" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1107,7 +1236,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1173,6 +1302,27 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1284,7 +1434,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="黑色浅色系标题行表格样式" count="2" xr9:uid="{1328B46F-2DFD-46DD-A77F-E8A23379C35A}">
+    <tableStyle name="黑色浅色系标题行表格样式" count="2" xr9:uid="{82D001B9-EF37-4DEE-81A5-608FF065D293}">
       <tableStyleElement type="wholeTable" dxfId="1"/>
       <tableStyleElement type="headerRow" dxfId="0"/>
     </tableStyle>
@@ -1659,44 +1809,89 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="3"/>
+  <dimension ref="A1:M7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6"/>
   <cols>
     <col min="1" max="1" width="9.84166666666667" customWidth="1"/>
-    <col min="2" max="2" width="12.3416666666667" customWidth="1"/>
-    <col min="3" max="3" width="10.3416666666667" customWidth="1"/>
-    <col min="4" max="4" width="18.25" customWidth="1"/>
+    <col min="2" max="2" width="10.3416666666667" customWidth="1"/>
+    <col min="3" max="3" width="12.3416666666667" customWidth="1"/>
+    <col min="4" max="4" width="10.3416666666667" customWidth="1"/>
+    <col min="5" max="5" width="23" customWidth="1"/>
+    <col min="6" max="6" width="10.3416666666667" customWidth="1"/>
+    <col min="7" max="7" width="7.125" customWidth="1"/>
+    <col min="12" max="12" width="11.25" customWidth="1"/>
+    <col min="13" max="13" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22.5" customHeight="1" spans="1:4">
+    <row r="1" ht="22.5" customHeight="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" ht="22.5" customHeight="1" spans="1:4">
+        <v>10</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
+      <c r="K1" s="23"/>
+      <c r="L1" s="23"/>
+      <c r="M1" s="23"/>
+    </row>
+    <row r="2" ht="22.5" customHeight="1" spans="1:13">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>5</v>
-      </c>
       <c r="D2" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" ht="22.5" customHeight="1" spans="1:4">
+        <v>13</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2" t="s">
+        <v>21</v>
+      </c>
+      <c r="M2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" ht="22.5" customHeight="1" spans="1:13">
       <c r="A3" s="5" t="s">
         <v>7</v>
       </c>
@@ -1709,22 +1904,91 @@
       <c r="D3" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" ht="39" customHeight="1" spans="1:4">
-      <c r="A4" s="7">
-        <v>1</v>
-      </c>
-      <c r="B4" s="8" t="s">
+      <c r="E3" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="K3" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="M3" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" ht="39" customHeight="1" spans="1:13">
+      <c r="A4" s="24">
+        <v>1</v>
+      </c>
+      <c r="B4" s="25">
+        <v>17</v>
+      </c>
+      <c r="C4" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="8">
-        <v>17</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>11</v>
-      </c>
+      <c r="D4" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" s="25">
+        <v>100</v>
+      </c>
+      <c r="G4">
+        <v>100</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>10</v>
+      </c>
+      <c r="M4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="5:6">
+      <c r="E5" s="28"/>
+      <c r="F5" s="28"/>
+    </row>
+    <row r="6" spans="5:6">
+      <c r="E6" s="28"/>
+      <c r="F6" s="28"/>
+    </row>
+    <row r="7" spans="5:6">
+      <c r="E7" s="28"/>
+      <c r="F7" s="28"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="F1:M1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
@@ -1732,6 +1996,94 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="3"/>
+  <cols>
+    <col min="1" max="1" width="14.875" customWidth="1"/>
+    <col min="2" max="2" width="17.125" customWidth="1"/>
+    <col min="3" max="3" width="13.625" customWidth="1"/>
+    <col min="4" max="4" width="12.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15" spans="1:4">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" ht="15" spans="1:4">
+      <c r="A2" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" ht="15" spans="1:4">
+      <c r="A3" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D13"/>
@@ -1791,13 +2143,13 @@
         <v>1</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="D4" s="20" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" ht="39" customHeight="1" spans="1:4">
@@ -1805,13 +2157,13 @@
         <v>2</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" ht="39" customHeight="1" spans="1:4">
@@ -1819,13 +2171,13 @@
         <v>3</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="D6" s="21" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1833,13 +2185,13 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="C7" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="D7" t="s">
-        <v>23</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1847,13 +2199,13 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="C8" t="s">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="D8" t="s">
-        <v>26</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1861,13 +2213,13 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="C9" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="D9" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1875,13 +2227,13 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>30</v>
+        <v>51</v>
       </c>
       <c r="C10" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="D10" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1889,13 +2241,13 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="C11" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="D11" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1903,13 +2255,13 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="C12" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="D12" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1917,13 +2269,13 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="C13" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="D13" t="s">
-        <v>41</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -1933,7 +2285,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D16"/>
@@ -1992,13 +2344,13 @@
         <v>1</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="C4" s="8">
         <v>1</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>43</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5" ht="22.5" customHeight="1" spans="1:4">
@@ -2006,13 +2358,13 @@
         <v>2</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="C5" s="8">
         <v>2</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>43</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6" ht="22.5" customHeight="1" spans="1:4">
@@ -2020,13 +2372,13 @@
         <v>3</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="C6" s="8">
         <v>3</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>46</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7" ht="22.5" customHeight="1" spans="1:4">
@@ -2034,13 +2386,13 @@
         <v>4</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>47</v>
+        <v>68</v>
       </c>
       <c r="C7" s="8">
         <v>4</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>43</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8" ht="22.5" customHeight="1" spans="1:4">
@@ -2048,13 +2400,13 @@
         <v>5</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="C8" s="8">
         <v>5</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>43</v>
+        <v>64</v>
       </c>
     </row>
     <row r="9" ht="36" customHeight="1" spans="1:4">
@@ -2062,13 +2414,13 @@
         <v>6</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>49</v>
+        <v>70</v>
       </c>
       <c r="C9" s="8">
         <v>6</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
     </row>
     <row r="10" ht="22.5" customHeight="1" spans="1:4">
@@ -2076,13 +2428,13 @@
         <v>7</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="C10" s="8">
         <v>7</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>52</v>
+        <v>73</v>
       </c>
     </row>
     <row r="11" ht="22.5" customHeight="1" spans="1:4">
@@ -2090,13 +2442,13 @@
         <v>8</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>53</v>
+        <v>74</v>
       </c>
       <c r="C11" s="8">
         <v>8</v>
       </c>
       <c r="D11" s="17" t="s">
-        <v>54</v>
+        <v>75</v>
       </c>
     </row>
     <row r="12" ht="22.5" customHeight="1" spans="1:4">
@@ -2104,13 +2456,13 @@
         <v>9</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>55</v>
+        <v>76</v>
       </c>
       <c r="C12" s="8">
         <v>9</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>56</v>
+        <v>77</v>
       </c>
     </row>
     <row r="13" ht="28" customHeight="1" spans="1:4">
@@ -2118,13 +2470,13 @@
         <v>10</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>57</v>
+        <v>78</v>
       </c>
       <c r="C13" s="8">
         <v>10</v>
       </c>
       <c r="D13" s="17" t="s">
-        <v>58</v>
+        <v>79</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2132,13 +2484,13 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="C14">
         <v>12</v>
       </c>
       <c r="D14" t="s">
-        <v>60</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2146,13 +2498,13 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>61</v>
+        <v>82</v>
       </c>
       <c r="C15">
         <v>13</v>
       </c>
       <c r="D15" t="s">
-        <v>62</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:4">
@@ -2160,13 +2512,13 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>63</v>
+        <v>84</v>
       </c>
       <c r="C16">
         <v>14</v>
       </c>
       <c r="D16" s="17" t="s">
-        <v>64</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>
@@ -2176,7 +2528,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E31"/>
@@ -2200,7 +2552,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>65</v>
+        <v>86</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>3</v>
@@ -2217,7 +2569,7 @@
         <v>5</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="E2" s="4" t="s">
         <v>6</v>
@@ -2234,7 +2586,7 @@
         <v>7</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>67</v>
+        <v>23</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>7</v>
@@ -2245,7 +2597,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="C4" s="8">
         <v>11</v>
@@ -2254,7 +2606,7 @@
         <v>1</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>69</v>
+        <v>89</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -2262,7 +2614,7 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="C5">
         <v>15</v>
@@ -2271,7 +2623,7 @@
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>71</v>
+        <v>91</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -2279,7 +2631,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="C6">
         <v>16</v>
@@ -2288,7 +2640,7 @@
         <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -2296,7 +2648,7 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="C7">
         <v>16</v>
@@ -2305,7 +2657,7 @@
         <v>1</v>
       </c>
       <c r="E7" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -2313,7 +2665,7 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="C8">
         <v>16</v>
@@ -2322,7 +2674,7 @@
         <v>1</v>
       </c>
       <c r="E8" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -2330,7 +2682,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="C9">
         <v>16</v>
@@ -2339,7 +2691,7 @@
         <v>1</v>
       </c>
       <c r="E9" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -2347,7 +2699,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="C10">
         <v>16</v>
@@ -2356,7 +2708,7 @@
         <v>1</v>
       </c>
       <c r="E10" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -2364,7 +2716,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>78</v>
+        <v>98</v>
       </c>
       <c r="C11">
         <v>16</v>
@@ -2373,7 +2725,7 @@
         <v>1</v>
       </c>
       <c r="E11" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -2381,7 +2733,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="C12">
         <v>16</v>
@@ -2390,7 +2742,7 @@
         <v>1</v>
       </c>
       <c r="E12" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -2398,7 +2750,7 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="C13">
         <v>16</v>
@@ -2407,7 +2759,7 @@
         <v>1</v>
       </c>
       <c r="E13" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -2415,7 +2767,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="C14">
         <v>16</v>
@@ -2424,7 +2776,7 @@
         <v>1</v>
       </c>
       <c r="E14" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -2432,7 +2784,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="C15">
         <v>16</v>
@@ -2441,7 +2793,7 @@
         <v>1</v>
       </c>
       <c r="E15" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -2449,7 +2801,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>83</v>
+        <v>103</v>
       </c>
       <c r="C16">
         <v>16</v>
@@ -2458,7 +2810,7 @@
         <v>1</v>
       </c>
       <c r="E16" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -2466,7 +2818,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="C17">
         <v>16</v>
@@ -2475,7 +2827,7 @@
         <v>1</v>
       </c>
       <c r="E17" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -2483,7 +2835,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="C18">
         <v>16</v>
@@ -2492,7 +2844,7 @@
         <v>1</v>
       </c>
       <c r="E18" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -2500,7 +2852,7 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="C19">
         <v>16</v>
@@ -2509,7 +2861,7 @@
         <v>1</v>
       </c>
       <c r="E19" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -2517,7 +2869,7 @@
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>87</v>
+        <v>107</v>
       </c>
       <c r="C20">
         <v>16</v>
@@ -2526,7 +2878,7 @@
         <v>1</v>
       </c>
       <c r="E20" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -2534,7 +2886,7 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>88</v>
+        <v>108</v>
       </c>
       <c r="C21">
         <v>16</v>
@@ -2543,7 +2895,7 @@
         <v>1</v>
       </c>
       <c r="E21" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -2551,7 +2903,7 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>89</v>
+        <v>109</v>
       </c>
       <c r="C22">
         <v>16</v>
@@ -2560,7 +2912,7 @@
         <v>1</v>
       </c>
       <c r="E22" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -2568,7 +2920,7 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="C23">
         <v>16</v>
@@ -2577,7 +2929,7 @@
         <v>1</v>
       </c>
       <c r="E23" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -2585,7 +2937,7 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>91</v>
+        <v>111</v>
       </c>
       <c r="C24">
         <v>16</v>
@@ -2594,7 +2946,7 @@
         <v>1</v>
       </c>
       <c r="E24" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -2602,7 +2954,7 @@
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>92</v>
+        <v>112</v>
       </c>
       <c r="C25">
         <v>16</v>
@@ -2611,7 +2963,7 @@
         <v>1</v>
       </c>
       <c r="E25" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -2619,7 +2971,7 @@
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>93</v>
+        <v>113</v>
       </c>
       <c r="C26">
         <v>16</v>
@@ -2628,7 +2980,7 @@
         <v>1</v>
       </c>
       <c r="E26" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -2636,7 +2988,7 @@
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>94</v>
+        <v>114</v>
       </c>
       <c r="C27">
         <v>16</v>
@@ -2645,7 +2997,7 @@
         <v>1</v>
       </c>
       <c r="E27" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -2653,7 +3005,7 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>95</v>
+        <v>115</v>
       </c>
       <c r="C28">
         <v>16</v>
@@ -2662,7 +3014,7 @@
         <v>1</v>
       </c>
       <c r="E28" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2670,7 +3022,7 @@
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="C29">
         <v>16</v>
@@ -2679,7 +3031,7 @@
         <v>1</v>
       </c>
       <c r="E29" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2687,7 +3039,7 @@
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>97</v>
+        <v>117</v>
       </c>
       <c r="C30">
         <v>16</v>
@@ -2696,7 +3048,7 @@
         <v>1</v>
       </c>
       <c r="E30" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2704,7 +3056,7 @@
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="C31">
         <v>16</v>
@@ -2713,7 +3065,7 @@
         <v>1</v>
       </c>
       <c r="E31" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>

--- a/server/xlsx/怪物表.xlsx
+++ b/server/xlsx/怪物表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28215" windowHeight="11640" firstSheet="3" activeTab="1"/>
+    <workbookView windowWidth="23310" windowHeight="12315" firstSheet="3" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="map_主神空间" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="122">
   <si>
     <t>id</t>
   </si>
@@ -70,6 +70,9 @@
     <t>主动技能</t>
   </si>
   <si>
+    <t>掉落物品</t>
+  </si>
+  <si>
     <t>属性基数</t>
   </si>
   <si>
@@ -79,6 +82,9 @@
     <t>sk_active</t>
   </si>
   <si>
+    <t>fall</t>
+  </si>
+  <si>
     <t>生命值</t>
   </si>
   <si>
@@ -101,6 +107,9 @@
   </si>
   <si>
     <t>魔法暴击率</t>
+  </si>
+  <si>
+    <t>Json</t>
   </si>
   <si>
     <t>Num</t>
@@ -111,6 +120,9 @@
   <si>
     <t>普通攻击as木头撞击
 普通攻击as木桩冲撞</t>
+  </si>
+  <si>
+    <t>[{"name":"树皮","min":1,"max":2,"wigth":100}]</t>
   </si>
   <si>
     <t>地图名称</t>
@@ -1236,7 +1248,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1302,6 +1314,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1434,7 +1449,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="黑色浅色系标题行表格样式" count="2" xr9:uid="{82D001B9-EF37-4DEE-81A5-608FF065D293}">
+    <tableStyle name="黑色浅色系标题行表格样式" count="2" xr9:uid="{B1DF475F-715B-42EC-BA63-8DFC0A7FE93F}">
       <tableStyleElement type="wholeTable" dxfId="1"/>
       <tableStyleElement type="headerRow" dxfId="0"/>
     </tableStyle>
@@ -1809,7 +1824,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6"/>
   <cols>
     <col min="1" max="1" width="9.84166666666667" customWidth="1"/>
@@ -1817,13 +1832,14 @@
     <col min="3" max="3" width="12.3416666666667" customWidth="1"/>
     <col min="4" max="4" width="10.3416666666667" customWidth="1"/>
     <col min="5" max="5" width="23" customWidth="1"/>
-    <col min="6" max="6" width="10.3416666666667" customWidth="1"/>
-    <col min="7" max="7" width="7.125" customWidth="1"/>
-    <col min="12" max="12" width="11.25" customWidth="1"/>
-    <col min="13" max="13" width="11" customWidth="1"/>
+    <col min="6" max="6" width="23.125" customWidth="1"/>
+    <col min="7" max="7" width="10.3416666666667" customWidth="1"/>
+    <col min="8" max="8" width="7.125" customWidth="1"/>
+    <col min="13" max="13" width="11.25" customWidth="1"/>
+    <col min="14" max="14" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22.5" customHeight="1" spans="1:13">
+    <row r="1" ht="22.5" customHeight="1" spans="1:14">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1842,15 +1858,18 @@
       <c r="F1" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
-      <c r="I1" s="23"/>
-      <c r="J1" s="23"/>
-      <c r="K1" s="23"/>
-      <c r="L1" s="23"/>
-      <c r="M1" s="23"/>
-    </row>
-    <row r="2" ht="22.5" customHeight="1" spans="1:13">
+      <c r="G1" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
+      <c r="J1" s="24"/>
+      <c r="K1" s="24"/>
+      <c r="L1" s="24"/>
+      <c r="M1" s="24"/>
+      <c r="N1" s="24"/>
+    </row>
+    <row r="2" ht="22.5" customHeight="1" spans="1:14">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
@@ -1861,37 +1880,40 @@
         <v>4</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G2" t="s">
         <v>16</v>
       </c>
+      <c r="G2" s="4" t="s">
+        <v>17</v>
+      </c>
       <c r="H2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="3" ht="22.5" customHeight="1" spans="1:13">
+        <v>23</v>
+      </c>
+      <c r="N2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" ht="22.5" customHeight="1" spans="1:14">
       <c r="A3" s="5" t="s">
         <v>7</v>
       </c>
@@ -1908,86 +1930,95 @@
         <v>7</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="L3" s="6" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M3" s="6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="4" ht="39" customHeight="1" spans="1:13">
-      <c r="A4" s="24">
-        <v>1</v>
-      </c>
-      <c r="B4" s="25">
+        <v>26</v>
+      </c>
+      <c r="N3" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" ht="39" customHeight="1" spans="1:14">
+      <c r="A4" s="25">
+        <v>1</v>
+      </c>
+      <c r="B4" s="26">
         <v>17</v>
       </c>
-      <c r="C4" s="26" t="s">
+      <c r="C4" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="27" t="s">
-        <v>24</v>
-      </c>
-      <c r="E4" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="F4" s="25">
+      <c r="D4" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="F4" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="G4" s="26">
         <v>100</v>
       </c>
-      <c r="G4">
+      <c r="H4">
         <v>100</v>
       </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
       <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4">
         <v>0</v>
       </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
       <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4">
         <v>0</v>
-      </c>
-      <c r="L4">
-        <v>10</v>
       </c>
       <c r="M4">
         <v>10</v>
       </c>
-    </row>
-    <row r="5" spans="5:6">
-      <c r="E5" s="28"/>
-      <c r="F5" s="28"/>
-    </row>
-    <row r="6" spans="5:6">
-      <c r="E6" s="28"/>
-      <c r="F6" s="28"/>
-    </row>
-    <row r="7" spans="5:6">
-      <c r="E7" s="28"/>
-      <c r="F7" s="28"/>
+      <c r="N4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="5:7">
+      <c r="E5" s="29"/>
+      <c r="F5" s="29"/>
+      <c r="G5" s="29"/>
+    </row>
+    <row r="6" spans="5:7">
+      <c r="E6" s="29"/>
+      <c r="F6" s="29"/>
+      <c r="G6" s="29"/>
+    </row>
+    <row r="7" spans="5:7">
+      <c r="E7" s="29"/>
+      <c r="F7" s="29"/>
+      <c r="G7" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="F1:M1"/>
+    <mergeCell ref="G1:N1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -2012,13 +2043,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" ht="15" spans="1:4">
@@ -2029,10 +2060,10 @@
         <v>4</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" ht="15" spans="1:4">
@@ -2043,18 +2074,18 @@
         <v>7</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B4" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -2065,10 +2096,10 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B5" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -2143,13 +2174,13 @@
         <v>1</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D4" s="20" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" ht="39" customHeight="1" spans="1:4">
@@ -2157,13 +2188,13 @@
         <v>2</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6" ht="39" customHeight="1" spans="1:4">
@@ -2171,13 +2202,13 @@
         <v>3</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D6" s="21" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2185,13 +2216,13 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C7" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D7" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2199,13 +2230,13 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C8" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D8" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2213,13 +2244,13 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C9" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D9" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2227,13 +2258,13 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C10" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D10" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2241,13 +2272,13 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C11" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D11" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2255,13 +2286,13 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C12" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="D12" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2269,13 +2300,13 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C13" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D13" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -2344,13 +2375,13 @@
         <v>1</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C4" s="8">
         <v>1</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="5" ht="22.5" customHeight="1" spans="1:4">
@@ -2358,13 +2389,13 @@
         <v>2</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C5" s="8">
         <v>2</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6" ht="22.5" customHeight="1" spans="1:4">
@@ -2372,13 +2403,13 @@
         <v>3</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C6" s="8">
         <v>3</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" ht="22.5" customHeight="1" spans="1:4">
@@ -2386,13 +2417,13 @@
         <v>4</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C7" s="8">
         <v>4</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="8" ht="22.5" customHeight="1" spans="1:4">
@@ -2400,13 +2431,13 @@
         <v>5</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C8" s="8">
         <v>5</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="9" ht="36" customHeight="1" spans="1:4">
@@ -2414,13 +2445,13 @@
         <v>6</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C9" s="8">
         <v>6</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
     </row>
     <row r="10" ht="22.5" customHeight="1" spans="1:4">
@@ -2428,13 +2459,13 @@
         <v>7</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C10" s="8">
         <v>7</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="11" ht="22.5" customHeight="1" spans="1:4">
@@ -2442,13 +2473,13 @@
         <v>8</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C11" s="8">
         <v>8</v>
       </c>
       <c r="D11" s="17" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="12" ht="22.5" customHeight="1" spans="1:4">
@@ -2456,13 +2487,13 @@
         <v>9</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C12" s="8">
         <v>9</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13" ht="28" customHeight="1" spans="1:4">
@@ -2470,13 +2501,13 @@
         <v>10</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C13" s="8">
         <v>10</v>
       </c>
       <c r="D13" s="17" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2484,13 +2515,13 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C14">
         <v>12</v>
       </c>
       <c r="D14" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2498,13 +2529,13 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C15">
         <v>13</v>
       </c>
       <c r="D15" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:4">
@@ -2512,13 +2543,13 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C16">
         <v>14</v>
       </c>
       <c r="D16" s="17" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -2552,7 +2583,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>3</v>
@@ -2569,7 +2600,7 @@
         <v>5</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="E2" s="4" t="s">
         <v>6</v>
@@ -2586,7 +2617,7 @@
         <v>7</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>7</v>
@@ -2597,7 +2628,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C4" s="8">
         <v>11</v>
@@ -2606,7 +2637,7 @@
         <v>1</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -2614,7 +2645,7 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C5">
         <v>15</v>
@@ -2623,7 +2654,7 @@
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -2631,7 +2662,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="C6">
         <v>16</v>
@@ -2640,7 +2671,7 @@
         <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -2648,7 +2679,7 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C7">
         <v>16</v>
@@ -2657,7 +2688,7 @@
         <v>1</v>
       </c>
       <c r="E7" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -2665,7 +2696,7 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C8">
         <v>16</v>
@@ -2674,7 +2705,7 @@
         <v>1</v>
       </c>
       <c r="E8" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -2682,7 +2713,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C9">
         <v>16</v>
@@ -2691,7 +2722,7 @@
         <v>1</v>
       </c>
       <c r="E9" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -2699,7 +2730,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="C10">
         <v>16</v>
@@ -2708,7 +2739,7 @@
         <v>1</v>
       </c>
       <c r="E10" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -2716,7 +2747,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C11">
         <v>16</v>
@@ -2725,7 +2756,7 @@
         <v>1</v>
       </c>
       <c r="E11" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -2733,7 +2764,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C12">
         <v>16</v>
@@ -2742,7 +2773,7 @@
         <v>1</v>
       </c>
       <c r="E12" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -2750,7 +2781,7 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C13">
         <v>16</v>
@@ -2759,7 +2790,7 @@
         <v>1</v>
       </c>
       <c r="E13" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -2767,7 +2798,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C14">
         <v>16</v>
@@ -2776,7 +2807,7 @@
         <v>1</v>
       </c>
       <c r="E14" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -2784,7 +2815,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C15">
         <v>16</v>
@@ -2793,7 +2824,7 @@
         <v>1</v>
       </c>
       <c r="E15" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -2801,7 +2832,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="C16">
         <v>16</v>
@@ -2810,7 +2841,7 @@
         <v>1</v>
       </c>
       <c r="E16" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -2818,7 +2849,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C17">
         <v>16</v>
@@ -2827,7 +2858,7 @@
         <v>1</v>
       </c>
       <c r="E17" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -2835,7 +2866,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C18">
         <v>16</v>
@@ -2844,7 +2875,7 @@
         <v>1</v>
       </c>
       <c r="E18" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -2852,7 +2883,7 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="C19">
         <v>16</v>
@@ -2861,7 +2892,7 @@
         <v>1</v>
       </c>
       <c r="E19" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -2869,7 +2900,7 @@
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C20">
         <v>16</v>
@@ -2878,7 +2909,7 @@
         <v>1</v>
       </c>
       <c r="E20" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -2886,7 +2917,7 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C21">
         <v>16</v>
@@ -2895,7 +2926,7 @@
         <v>1</v>
       </c>
       <c r="E21" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -2903,7 +2934,7 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="C22">
         <v>16</v>
@@ -2912,7 +2943,7 @@
         <v>1</v>
       </c>
       <c r="E22" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -2920,7 +2951,7 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="C23">
         <v>16</v>
@@ -2929,7 +2960,7 @@
         <v>1</v>
       </c>
       <c r="E23" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -2937,7 +2968,7 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="C24">
         <v>16</v>
@@ -2946,7 +2977,7 @@
         <v>1</v>
       </c>
       <c r="E24" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -2954,7 +2985,7 @@
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C25">
         <v>16</v>
@@ -2963,7 +2994,7 @@
         <v>1</v>
       </c>
       <c r="E25" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -2971,7 +3002,7 @@
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C26">
         <v>16</v>
@@ -2980,7 +3011,7 @@
         <v>1</v>
       </c>
       <c r="E26" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -2988,7 +3019,7 @@
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="C27">
         <v>16</v>
@@ -2997,7 +3028,7 @@
         <v>1</v>
       </c>
       <c r="E27" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -3005,7 +3036,7 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="C28">
         <v>16</v>
@@ -3014,7 +3045,7 @@
         <v>1</v>
       </c>
       <c r="E28" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -3022,7 +3053,7 @@
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="C29">
         <v>16</v>
@@ -3031,7 +3062,7 @@
         <v>1</v>
       </c>
       <c r="E29" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -3039,7 +3070,7 @@
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C30">
         <v>16</v>
@@ -3048,7 +3079,7 @@
         <v>1</v>
       </c>
       <c r="E30" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -3056,7 +3087,7 @@
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="C31">
         <v>16</v>
@@ -3065,7 +3096,7 @@
         <v>1</v>
       </c>
       <c r="E31" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
